--- a/scenarios/CULandDRY_COWS.xlsx
+++ b/scenarios/CULandDRY_COWS.xlsx
@@ -152,8 +152,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -229,7 +230,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -240,6 +240,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,14 +578,14 @@
       <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <f>K2</f>
         <v>9052</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="8">
         <v>10025.4</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="9">
         <v>9052</v>
       </c>
       <c r="L2" t="s">
@@ -604,14 +605,14 @@
       <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <f>K3</f>
         <v>8284</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>9367.2000000000007</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>8284</v>
       </c>
       <c r="L3" t="s">
@@ -638,7 +639,7 @@
       <c r="J5">
         <v>13.2</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <f>12 / (K25 / (K23/12))</f>
         <v>14.602499999999997</v>
       </c>
@@ -666,7 +667,7 @@
       <c r="J6">
         <v>12.9</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <f>12 / (K26 / (K24/12))</f>
         <v>14.580909090909088</v>
       </c>
@@ -694,7 +695,7 @@
       <c r="J8">
         <v>37.1</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="11">
         <v>35.799999999999997</v>
       </c>
       <c r="L8" t="s">
@@ -721,7 +722,7 @@
       <c r="J9">
         <v>36.1</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="11">
         <v>34.799999999999997</v>
       </c>
       <c r="L9" t="s">
@@ -751,7 +752,7 @@
       <c r="J11" s="4">
         <v>651.52821361702138</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="12">
         <f>J11</f>
         <v>651.52821361702138</v>
       </c>
@@ -812,7 +813,7 @@
       <c r="J14" s="1">
         <v>6.6079520088655128</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <v>16.706</v>
       </c>
     </row>
@@ -829,9 +830,9 @@
       <c r="G15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="7">
-        <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
-        <v>0.89047832318622011</v>
+      <c r="H15" s="15">
+        <f>(1 / (100 - J14)) * (1 - K14/100) * 100</f>
+        <v>0.8918746487699567</v>
       </c>
       <c r="J15" s="1"/>
     </row>
@@ -864,7 +865,7 @@
       <c r="J16" s="1">
         <v>6.4615074492035101</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="10">
         <v>16.706</v>
       </c>
     </row>
@@ -887,14 +888,14 @@
       <c r="G17" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="7">
-        <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
+      <c r="H17" s="15">
+        <f>(1 / (100 - J16)) * (1 - K16/100) * 100</f>
         <v>0.89047832318622011</v>
       </c>
       <c r="J17" s="1"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>40</v>
       </c>
       <c r="I19" t="s">
@@ -903,7 +904,7 @@
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="11">
         <v>0.25</v>
       </c>
     </row>
@@ -914,12 +915,12 @@
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="11">
         <v>0.25</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>39</v>
       </c>
       <c r="I21" t="s">
@@ -928,7 +929,7 @@
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="11">
         <v>6</v>
       </c>
     </row>
@@ -939,12 +940,12 @@
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="11">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I23" t="s">
@@ -953,7 +954,7 @@
       <c r="J23" s="1">
         <v>32</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="10">
         <v>35.4</v>
       </c>
     </row>
@@ -964,7 +965,7 @@
       <c r="J24" s="1">
         <v>33</v>
       </c>
-      <c r="K24" s="11">
+      <c r="K24" s="10">
         <v>37.299999999999997</v>
       </c>
     </row>
@@ -979,7 +980,7 @@
         <f>(12/J5) * (J23/12)</f>
         <v>2.4242424242424243</v>
       </c>
-      <c r="K25" s="15">
+      <c r="K25" s="14">
         <f>J25</f>
         <v>2.4242424242424243</v>
       </c>
@@ -992,7 +993,7 @@
         <f>(12/J6) * (J24/12)</f>
         <v>2.558139534883721</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="14">
         <f>J26</f>
         <v>2.558139534883721</v>
       </c>
@@ -1047,7 +1048,7 @@
       <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>41</v>
       </c>
     </row>

--- a/scenarios/CULandDRY_COWS.xlsx
+++ b/scenarios/CULandDRY_COWS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
   <si>
     <t>parameter</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>new</t>
+  </si>
+  <si>
+    <t>all other feeds reduced proportionally</t>
   </si>
 </sst>
 </file>
@@ -154,7 +157,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -240,7 +243,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,13 +693,13 @@
       </c>
       <c r="H8" s="1">
         <f>K8</f>
-        <v>35.799999999999997</v>
+        <v>33.9</v>
       </c>
       <c r="J8">
         <v>37.1</v>
       </c>
       <c r="K8" s="11">
-        <v>35.799999999999997</v>
+        <v>33.9</v>
       </c>
       <c r="L8" t="s">
         <v>27</v>
@@ -717,13 +720,13 @@
       </c>
       <c r="H9" s="1">
         <f>K9</f>
-        <v>34.799999999999997</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="J9">
         <v>36.1</v>
       </c>
       <c r="K9" s="11">
-        <v>34.799999999999997</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="L9" t="s">
         <v>27</v>
@@ -808,13 +811,13 @@
       </c>
       <c r="H14" s="1">
         <f>K14</f>
-        <v>16.706</v>
+        <v>12.1</v>
       </c>
       <c r="J14" s="1">
         <v>6.6079520088655128</v>
       </c>
       <c r="K14" s="10">
-        <v>16.706</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -832,9 +835,11 @@
       </c>
       <c r="H15" s="15">
         <f>(1 / (100 - J14)) * (1 - K14/100) * 100</f>
-        <v>0.8918746487699567</v>
-      </c>
-      <c r="J15" s="1"/>
+        <v>0.94119362291256503</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -860,13 +865,13 @@
       </c>
       <c r="H16" s="1">
         <f>K16</f>
-        <v>16.706</v>
+        <v>12.1</v>
       </c>
       <c r="J16" s="1">
         <v>6.4615074492035101</v>
       </c>
       <c r="K16" s="10">
-        <v>16.706</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -890,9 +895,11 @@
       </c>
       <c r="H17" s="15">
         <f>(1 / (100 - J16)) * (1 - K16/100) * 100</f>
-        <v>0.89047832318622011</v>
-      </c>
-      <c r="J17" s="1"/>
+        <v>0.93972008317608402</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H19" s="7" t="s">
@@ -1076,13 +1083,13 @@
       </c>
       <c r="H2" s="4">
         <f>K2</f>
-        <v>64.132999999999996</v>
+        <v>74</v>
       </c>
       <c r="J2" s="2">
         <v>20</v>
       </c>
       <c r="K2" s="4">
-        <v>64.132999999999996</v>
+        <v>74</v>
       </c>
       <c r="L2" t="s">
         <v>27</v>

--- a/scenarios/CULandDRY_COWS.xlsx
+++ b/scenarios/CULandDRY_COWS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
   <si>
     <t>parameter</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>recruitment_rate</t>
-  </si>
-  <si>
-    <t>ret.</t>
   </si>
   <si>
     <t>cattle</t>
@@ -225,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -244,6 +241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,7 +542,7 @@
         <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>8</v>
@@ -565,7 +563,7 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -592,7 +590,7 @@
         <v>9052</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -619,7 +617,7 @@
         <v>8284</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -647,7 +645,7 @@
         <v>14.602499999999997</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -675,7 +673,7 @@
         <v>14.580909090909088</v>
       </c>
       <c r="L6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -702,7 +700,7 @@
         <v>33.9</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -729,7 +727,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -742,7 +740,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>2</v>
@@ -760,7 +758,7 @@
         <v>651.52821361702138</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M11" s="6"/>
     </row>
@@ -779,7 +777,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -831,14 +829,14 @@
         <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H15" s="15">
         <f>(1 / (100 - J14)) * (1 - K14/100) * 100</f>
         <v>0.94119362291256503</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -849,7 +847,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -882,7 +880,7 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -891,22 +889,22 @@
         <v>6</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H17" s="15">
         <f>(1 / (100 - J16)) * (1 - K16/100) * 100</f>
         <v>0.93972008317608402</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H19" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -917,7 +915,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -928,10 +926,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H21" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -942,7 +940,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -953,10 +951,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" t="s">
         <v>35</v>
-      </c>
-      <c r="I23" t="s">
-        <v>36</v>
       </c>
       <c r="J23" s="1">
         <v>32</v>
@@ -967,7 +965,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J24" s="1">
         <v>33</v>
@@ -978,10 +976,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J25" s="1">
         <f>(12/J5) * (J23/12)</f>
@@ -994,7 +992,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J26" s="1">
         <f>(12/J6) * (J24/12)</f>
@@ -1029,7 +1027,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
@@ -1038,10 +1036,10 @@
         <v>8</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
@@ -1056,12 +1054,12 @@
         <v>16</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -1070,32 +1068,32 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="4">
         <f>K2</f>
-        <v>74</v>
+        <v>74.05</v>
       </c>
       <c r="J2" s="2">
         <v>20</v>
       </c>
-      <c r="K2" s="4">
-        <v>74</v>
+      <c r="K2" s="16">
+        <v>74.05</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios/CULandDRY_COWS.xlsx
+++ b/scenarios/CULandDRY_COWS.xlsx
@@ -1,26 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39F2ED7-E63F-41C9-9082-F64D0F3647E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CattleHerd" sheetId="4" r:id="rId1"/>
     <sheet name="FeedMgmt" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="40">
   <si>
     <t>parameter</t>
   </si>
@@ -134,12 +146,6 @@
   </si>
   <si>
     <t># calves</t>
-  </si>
-  <si>
-    <t>delayed culling</t>
-  </si>
-  <si>
-    <t>share of cows</t>
   </si>
   <si>
     <t>new</t>
@@ -151,7 +157,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
@@ -222,23 +228,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -521,8 +524,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -534,7 +537,7 @@
     <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -563,10 +566,10 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -579,21 +582,22 @@
       <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <f>K2</f>
-        <v>9052</v>
-      </c>
-      <c r="J2" s="8">
-        <v>10025.4</v>
-      </c>
-      <c r="K2" s="9">
-        <v>9052</v>
+        <v>8764.5571059137801</v>
+      </c>
+      <c r="J2" s="7">
+        <v>9638</v>
+      </c>
+      <c r="K2" s="8">
+        <f>J2/(K19/J19)</f>
+        <v>8764.5571059137801</v>
       </c>
       <c r="L2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -606,21 +610,22 @@
       <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <f>K3</f>
-        <v>8284</v>
-      </c>
-      <c r="J3" s="8">
-        <v>9367.2000000000007</v>
-      </c>
-      <c r="K3" s="9">
-        <v>8284</v>
+        <v>8017.6181739693493</v>
+      </c>
+      <c r="J3" s="7">
+        <v>9005</v>
+      </c>
+      <c r="K3" s="8">
+        <f>J3/(K20/J20)</f>
+        <v>8017.6181739693493</v>
       </c>
       <c r="L3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -635,20 +640,20 @@
       </c>
       <c r="H5" s="1">
         <f>K5</f>
-        <v>14.602499999999997</v>
+        <v>14.5154625</v>
       </c>
       <c r="J5">
         <v>13.2</v>
       </c>
-      <c r="K5" s="10">
-        <f>12 / (K25 / (K23/12))</f>
-        <v>14.602499999999997</v>
+      <c r="K5" s="9">
+        <f>12 / (K21 / (K19/12))</f>
+        <v>14.5154625</v>
       </c>
       <c r="L5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -663,20 +668,20 @@
       </c>
       <c r="H6" s="1">
         <f>K6</f>
-        <v>14.580909090909088</v>
+        <v>14.488654545454544</v>
       </c>
       <c r="J6">
         <v>12.9</v>
       </c>
-      <c r="K6" s="10">
-        <f>12 / (K26 / (K24/12))</f>
-        <v>14.580909090909088</v>
+      <c r="K6" s="9">
+        <f>12 / (K22 / (K20/12))</f>
+        <v>14.488654545454544</v>
       </c>
       <c r="L6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -691,19 +696,20 @@
       </c>
       <c r="H8" s="1">
         <f>K8</f>
-        <v>33.9</v>
+        <v>34.101565830231038</v>
       </c>
       <c r="J8">
         <v>37.1</v>
       </c>
-      <c r="K8" s="11">
-        <v>33.9</v>
+      <c r="K8" s="9">
+        <f>12/K19*100</f>
+        <v>34.101565830231038</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -718,19 +724,20 @@
       </c>
       <c r="H9" s="1">
         <f>K9</f>
-        <v>32.200000000000003</v>
+        <v>32.376429958989853</v>
       </c>
       <c r="J9">
         <v>36.1</v>
       </c>
-      <c r="K9" s="11">
-        <v>32.200000000000003</v>
+      <c r="K9" s="9">
+        <f>12/K20*100</f>
+        <v>32.376429958989853</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -753,16 +760,15 @@
       <c r="J11" s="4">
         <v>651.52821361702138</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="10">
         <f>J11</f>
         <v>651.52821361702138</v>
       </c>
       <c r="L11" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -773,9 +779,8 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="4"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>32</v>
       </c>
@@ -789,9 +794,8 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="4"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -809,16 +813,16 @@
       </c>
       <c r="H14" s="1">
         <f>K14</f>
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="J14" s="1">
         <v>6.6079520088655128</v>
       </c>
-      <c r="K14" s="10">
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K14" s="9">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -831,15 +835,15 @@
       <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="12">
         <f>(1 / (100 - J14)) * (1 - K14/100) * 100</f>
-        <v>0.94119362291256503</v>
+        <v>0.93476909306333245</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -863,13 +867,13 @@
       </c>
       <c r="H16" s="1">
         <f>K16</f>
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="J16" s="1">
         <v>6.4615074492035101</v>
       </c>
-      <c r="K16" s="10">
-        <v>12.1</v>
+      <c r="K16" s="9">
+        <v>12.7</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -891,115 +895,65 @@
       <c r="G17" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="12">
         <f>(1 / (100 - J16)) * (1 - K16/100) * 100</f>
-        <v>0.93972008317608402</v>
+        <v>0.93330561161856818</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H19" s="7" t="s">
-        <v>39</v>
+      <c r="H19" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="I19" t="s">
         <v>35</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="11">
-        <v>0.25</v>
+      <c r="J19" s="1">
+        <v>32</v>
+      </c>
+      <c r="K19" s="9">
+        <v>35.189</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
         <v>36</v>
       </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="11">
-        <v>0.25</v>
+      <c r="J20" s="1">
+        <v>33</v>
+      </c>
+      <c r="K20" s="9">
+        <v>37.064</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H21" s="7" t="s">
-        <v>38</v>
+      <c r="H21" t="s">
+        <v>37</v>
       </c>
       <c r="I21" t="s">
         <v>35</v>
       </c>
-      <c r="J21">
-        <v>0</v>
+      <c r="J21" s="1">
+        <f>(12/J5) * (J19/12)</f>
+        <v>2.4242424242424243</v>
       </c>
       <c r="K21" s="11">
-        <v>6</v>
+        <f>J21</f>
+        <v>2.4242424242424243</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
         <v>36</v>
       </c>
-      <c r="J22">
-        <v>0</v>
+      <c r="J22" s="1">
+        <f>(12/J6) * (J20/12)</f>
+        <v>2.558139534883721</v>
       </c>
       <c r="K22" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="1">
-        <v>32</v>
-      </c>
-      <c r="K23" s="10">
-        <v>35.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I24" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="1">
-        <v>33</v>
-      </c>
-      <c r="K24" s="10">
-        <v>37.299999999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H25" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="1">
-        <f>(12/J5) * (J23/12)</f>
-        <v>2.4242424242424243</v>
-      </c>
-      <c r="K25" s="14">
-        <f>J25</f>
-        <v>2.4242424242424243</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I26" t="s">
-        <v>36</v>
-      </c>
-      <c r="J26" s="1">
-        <f>(12/J6) * (J24/12)</f>
-        <v>2.558139534883721</v>
-      </c>
-      <c r="K26" s="14">
-        <f>J26</f>
+        <f>J22</f>
         <v>2.558139534883721</v>
       </c>
     </row>
@@ -1010,7 +964,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1053,8 +1007,8 @@
       <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="13" t="s">
-        <v>40</v>
+      <c r="K1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1081,13 +1035,13 @@
       </c>
       <c r="H2" s="4">
         <f>K2</f>
-        <v>74.05</v>
+        <v>68</v>
       </c>
       <c r="J2" s="2">
-        <v>20</v>
-      </c>
-      <c r="K2" s="16">
-        <v>74.05</v>
+        <v>28</v>
+      </c>
+      <c r="K2" s="13">
+        <v>68</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>

--- a/scenarios/CULandDRY_COWS.xlsx
+++ b/scenarios/CULandDRY_COWS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39F2ED7-E63F-41C9-9082-F64D0F3647E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7024794-AE3D-4601-AF46-E076F4D9FDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2310" yWindow="2460" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CattleHerd" sheetId="4" r:id="rId1"/>
@@ -85,9 +85,6 @@
     <t>orig.</t>
   </si>
   <si>
-    <t>recruitment_rate</t>
-  </si>
-  <si>
     <t>cattle</t>
   </si>
   <si>
@@ -152,6 +149,9 @@
   </si>
   <si>
     <t>all other feeds reduced proportionally</t>
+  </si>
+  <si>
+    <t>replacement_rate</t>
   </si>
 </sst>
 </file>
@@ -545,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>8</v>
@@ -566,7 +566,7 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -594,7 +594,7 @@
         <v>8764.5571059137801</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -622,7 +622,7 @@
         <v>8017.6181739693493</v>
       </c>
       <c r="L3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -650,7 +650,7 @@
         <v>14.5154625</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -678,7 +678,7 @@
         <v>14.488654545454544</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -689,7 +689,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>2</v>
@@ -706,7 +706,7 @@
         <v>34.101565830231038</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -717,7 +717,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
         <v>2</v>
@@ -734,7 +734,7 @@
         <v>32.376429958989853</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -747,7 +747,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>2</v>
@@ -765,7 +765,7 @@
         <v>651.52821361702138</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -782,7 +782,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -833,14 +833,14 @@
         <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H15" s="12">
         <f>(1 / (100 - J14)) * (1 - K14/100) * 100</f>
         <v>0.93476909306333245</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -851,7 +851,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -884,7 +884,7 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -893,22 +893,22 @@
         <v>6</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H17" s="12">
         <f>(1 / (100 - J16)) * (1 - K16/100) * 100</f>
         <v>0.93330561161856818</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" t="s">
         <v>34</v>
-      </c>
-      <c r="I19" t="s">
-        <v>35</v>
       </c>
       <c r="J19" s="1">
         <v>32</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J20" s="1">
         <v>33</v>
@@ -930,10 +930,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J21" s="1">
         <f>(12/J5) * (J19/12)</f>
@@ -946,7 +946,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J22" s="1">
         <f>(12/J6) * (J20/12)</f>
@@ -981,7 +981,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
@@ -990,10 +990,10 @@
         <v>8</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
@@ -1008,12 +1008,12 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -1022,13 +1022,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
@@ -1044,10 +1044,10 @@
         <v>68</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios/CULandDRY_COWS.xlsx
+++ b/scenarios/CULandDRY_COWS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7024794-AE3D-4601-AF46-E076F4D9FDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD7B3B1-CB7B-4FC4-98FC-A9203ADE665B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="2460" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36585" yWindow="-960" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CattleHerd" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="41">
   <si>
     <t>parameter</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>replacement_rate</t>
+  </si>
+  <si>
+    <t>&lt;-- Same %-unit increase as conventional</t>
   </si>
 </sst>
 </file>
@@ -162,7 +165,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,6 +210,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -228,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -245,6 +256,8 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -590,7 +603,7 @@
         <v>9638</v>
       </c>
       <c r="K2" s="8">
-        <f>J2/(K19/J19)</f>
+        <f>J2/(K21/J21)</f>
         <v>8764.5571059137801</v>
       </c>
       <c r="L2" t="s">
@@ -618,7 +631,7 @@
         <v>9005</v>
       </c>
       <c r="K3" s="8">
-        <f>J3/(K20/J20)</f>
+        <f>J3/(K22/J22)</f>
         <v>8017.6181739693493</v>
       </c>
       <c r="L3" t="s">
@@ -646,7 +659,7 @@
         <v>13.2</v>
       </c>
       <c r="K5" s="9">
-        <f>12 / (K21 / (K19/12))</f>
+        <f>12 / (K23 / (K21/12))</f>
         <v>14.5154625</v>
       </c>
       <c r="L5" t="s">
@@ -674,7 +687,7 @@
         <v>12.9</v>
       </c>
       <c r="K6" s="9">
-        <f>12 / (K22 / (K20/12))</f>
+        <f>12 / (K24 / (K22/12))</f>
         <v>14.488654545454544</v>
       </c>
       <c r="L6" t="s">
@@ -702,7 +715,7 @@
         <v>37.1</v>
       </c>
       <c r="K8" s="9">
-        <f>12/K19*100</f>
+        <f>12/K21*100</f>
         <v>34.101565830231038</v>
       </c>
       <c r="L8" t="s">
@@ -730,7 +743,7 @@
         <v>36.1</v>
       </c>
       <c r="K9" s="9">
-        <f>12/K20*100</f>
+        <f>12/K22*100</f>
         <v>32.376429958989853</v>
       </c>
       <c r="L9" t="s">
@@ -799,6 +812,9 @@
       <c r="A14" t="s">
         <v>4</v>
       </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
@@ -826,6 +842,9 @@
       <c r="A15" t="s">
         <v>4</v>
       </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
@@ -835,7 +854,7 @@
       <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="15">
         <f>(1 / (100 - J14)) * (1 - K14/100) * 100</f>
         <v>0.93476909306333245</v>
       </c>
@@ -848,10 +867,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -867,13 +883,17 @@
       </c>
       <c r="H16" s="1">
         <f>K16</f>
-        <v>12.7</v>
+        <v>16.889458206396505</v>
       </c>
       <c r="J16" s="1">
-        <v>6.4615074492035101</v>
+        <v>10.797410215262019</v>
       </c>
       <c r="K16" s="9">
-        <v>12.7</v>
+        <f>J16+(K14-J14)</f>
+        <v>16.889458206396505</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -881,10 +901,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -895,53 +912,86 @@
       <c r="G17" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="12">
-        <f>(1 / (100 - J16)) * (1 - K16/100) * 100</f>
-        <v>0.93330561161856818</v>
+      <c r="H17" s="15">
+        <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
+        <v>0.93170548068351267</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="1">
+        <f>K18</f>
+        <v>12.7</v>
+      </c>
+      <c r="J18" s="1">
+        <v>6.4615074492035101</v>
+      </c>
+      <c r="K18" s="9">
+        <v>12.7</v>
+      </c>
+    </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H19" s="6" t="s">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="12">
+        <f>(1 / (100 - J18)) * (1 - K18/100) * 100</f>
+        <v>0.93330561161856818</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H21" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="I19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J19" s="1">
-        <v>32</v>
-      </c>
-      <c r="K19" s="9">
-        <v>35.189</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I20" t="s">
-        <v>35</v>
-      </c>
-      <c r="J20" s="1">
-        <v>33</v>
-      </c>
-      <c r="K20" s="9">
-        <v>37.064</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H21" t="s">
-        <v>36</v>
       </c>
       <c r="I21" t="s">
         <v>34</v>
       </c>
       <c r="J21" s="1">
-        <f>(12/J5) * (J19/12)</f>
-        <v>2.4242424242424243</v>
-      </c>
-      <c r="K21" s="11">
-        <f>J21</f>
-        <v>2.4242424242424243</v>
+        <v>32</v>
+      </c>
+      <c r="K21" s="9">
+        <v>35.189</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -949,11 +999,38 @@
         <v>35</v>
       </c>
       <c r="J22" s="1">
-        <f>(12/J6) * (J20/12)</f>
+        <v>33</v>
+      </c>
+      <c r="K22" s="9">
+        <v>37.064</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="1">
+        <f>(12/J5) * (J21/12)</f>
+        <v>2.4242424242424243</v>
+      </c>
+      <c r="K23" s="11">
+        <f>J23</f>
+        <v>2.4242424242424243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="1">
+        <f>(12/J6) * (J22/12)</f>
         <v>2.558139534883721</v>
       </c>
-      <c r="K22" s="11">
-        <f>J22</f>
+      <c r="K24" s="11">
+        <f>J24</f>
         <v>2.558139534883721</v>
       </c>
     </row>
